--- a/1-LATEX/2-DADOS/3-OUTPUT/sensibilidade_DL_REML.xlsx
+++ b/1-LATEX/2-DADOS/3-OUTPUT/sensibilidade_DL_REML.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.02121684598240538</v>
+        <v>0.02389601709455585</v>
       </c>
       <c r="C3">
-        <v>0.04486936865596249</v>
+        <v>0.01655094282820235</v>
       </c>
       <c r="D3">
-        <v>0.01500483635229927</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0.05019368857278299</v>
+        <v>0.09809679900415691</v>
       </c>
       <c r="F3">
-        <v>-0.006212009630106111</v>
+        <v>-0.02389601709455585</v>
       </c>
       <c r="G3">
-        <v>0.005324319916820502</v>
+        <v>0.08154585617595456</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.02766083366641499</v>
+        <v>0.09260327465062979</v>
       </c>
       <c r="C4">
-        <v>0.0715762333288117</v>
+        <v>0.007406689765167936</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.003853065935056671</v>
       </c>
       <c r="E4">
-        <v>0.1978870688222608</v>
+        <v>0.06321986839947043</v>
       </c>
       <c r="F4">
-        <v>-0.02766083366641499</v>
+        <v>-0.08875020871557311</v>
       </c>
       <c r="G4">
-        <v>0.1263108354934491</v>
+        <v>0.05581317863430249</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.09260327465062979</v>
+        <v>0.1706084965332423</v>
       </c>
       <c r="C5">
-        <v>0.007406689765167936</v>
+        <v>-0.2787297834861159</v>
       </c>
       <c r="D5">
-        <v>0.003853065935056671</v>
+        <v>0.3180900648897915</v>
       </c>
       <c r="E5">
-        <v>0.06321986839947043</v>
+        <v>-0.2767563033950527</v>
       </c>
       <c r="F5">
-        <v>-0.08875020871557311</v>
+        <v>0.1474815683565492</v>
       </c>
       <c r="G5">
-        <v>0.05581317863430249</v>
+        <v>0.001973480091063184</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.1706084965332423</v>
+        <v>0.101150822222562</v>
       </c>
       <c r="C6">
-        <v>-0.2787297834861159</v>
+        <v>0.1716000516464709</v>
       </c>
       <c r="D6">
-        <v>0.3180900648897915</v>
+        <v>0.01943131468833286</v>
       </c>
       <c r="E6">
-        <v>-0.2767563033950527</v>
+        <v>0.163361639116147</v>
       </c>
       <c r="F6">
-        <v>0.1474815683565492</v>
+        <v>-0.08171950753422916</v>
       </c>
       <c r="G6">
-        <v>0.001973480091063184</v>
+        <v>-0.008238412530323841</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,72 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.101150822222562</v>
+        <v>2.991635273407584E-09</v>
       </c>
       <c r="C7">
-        <v>0.1716000516464709</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0.01943131468833286</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0.163361639116147</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>-0.08171950753422916</v>
+        <v>-2.991635273407584E-09</v>
       </c>
       <c r="G7">
-        <v>-0.008238412530323841</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>2.050008407799427E-09</v>
+      </c>
+      <c r="C8">
+        <v>0.05120757691971459</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0.05120757701632275</v>
+      </c>
+      <c r="F8">
+        <v>-2.050008407799427E-09</v>
+      </c>
+      <c r="G8">
+        <v>9.660815897261088E-11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>4.655057934973063E-10</v>
+      </c>
+      <c r="C9">
+        <v>0.2796759127099698</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0.2796759134695573</v>
+      </c>
+      <c r="F9">
+        <v>-4.655057934973063E-10</v>
+      </c>
+      <c r="G9">
+        <v>7.595875595178825E-10</v>
       </c>
     </row>
   </sheetData>
